--- a/web/files/港岛-坚尼地城及摩星岭-吉喆.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-吉喆.xlsx
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>5751000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>19628</v>
+        <v>19561</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
           <t>A | 1012呎 (3房)
 $4100万
 $40,514/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -8888,7 +8888,7 @@
           <t>D | 406呎 (1房)
 $993万
 $24,458/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
@@ -8909,7 +8909,7 @@
           <t>A | 1012呎 (3房)
 $3196万
 $31,581/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -8917,7 +8917,7 @@
           <t>B | 821呎 (3房)
 $2545万
 $31,000/呎
-(25年-04月)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8925,7 +8925,7 @@
           <t>C | 979呎 (3房)
 $3084万
 $31,499/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -8933,7 +8933,7 @@
           <t>D | 406呎 (1房)
 $986万
 $24,286/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr"/>
@@ -8954,7 +8954,7 @@
           <t>A | 1012呎 (3房)
 $3340万
 $33,000/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -8978,7 +8978,7 @@
           <t>D | 406呎 (1房)
 $978万
 $24,089/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -8999,7 +8999,7 @@
           <t>A | 1012呎 (3房)
 $3137万
 $31,000/呎
-(24年-07月)</t>
+(24年-07月-23日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -9015,7 +9015,7 @@
           <t>C | 979呎 (3房)
 $3024万
 $30,888/呎
-(24年-07月)</t>
+(24年-07月-09日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -9023,7 +9023,7 @@
           <t>D | 406呎 (1房)
 $971万
 $23,916/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr"/>
@@ -9044,7 +9044,7 @@
           <t>A | 1012呎 (3房)
 $3076万
 $30,400/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -9052,7 +9052,7 @@
           <t>B | 821呎 (3房)
 $2482万
 $30,231/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -9060,7 +9060,7 @@
           <t>C | 978呎 (3房)
 $2980万
 $30,470/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -9068,7 +9068,7 @@
           <t>D | 406呎 (1房)
 $964万
 $23,744/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
           <t>A | 1012呎 (3房)
 $3066万
 $30,300/呎
-(25年-06月)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -9097,7 +9097,7 @@
           <t>B | 821呎 (3房)
 $2459万
 $29,946/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -9113,7 +9113,7 @@
           <t>D | 406呎 (1房)
 $957万
 $23,571/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr"/>
@@ -9134,7 +9134,7 @@
           <t>A | 524呎 (2房)
 $1479万
 $28,221/呎
-(24年-09月)</t>
+(24年-09月-15日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -9142,7 +9142,7 @@
           <t>B | 386呎 (1房)
 $1065万
 $27,601/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -9150,7 +9150,7 @@
           <t>C | 382呎 (1房)
 $1005万
 $26,309/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -9158,7 +9158,7 @@
           <t>D | 297呎 (开放式)
 $795万
 $26,771/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -9166,7 +9166,7 @@
           <t>E | 220呎 (开放式)
 $501万
 $22,773/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -9174,7 +9174,7 @@
           <t>F | 293呎 (开放式)
 $628万
 $21,447/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -9182,7 +9182,7 @@
           <t>G | 266呎 (开放式)
 $541万
 $20,342/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -9190,7 +9190,7 @@
           <t>H | 252呎 (开放式)
 $512万
 $20,337/呎
-(24年-09月)</t>
+(24年-09月-18日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -9198,7 +9198,7 @@
           <t>J | 211呎 (开放式)
 $430万
 $20,393/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -9206,7 +9206,7 @@
           <t>K | 370呎 (1房)
 $862万
 $23,297/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
           <t>A | 524呎 (2房)
 $1483万
 $28,303/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -9229,7 +9229,7 @@
           <t>B | 386呎 (1房)
 $1068万
 $27,666/呎
-(25年-06月)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -9237,7 +9237,7 @@
           <t>C | 382呎 (1房)
 $1007万
 $26,366/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -9245,7 +9245,7 @@
           <t>D | 297呎 (开放式)
 $789万
 $26,566/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -9253,7 +9253,7 @@
           <t>E | 220呎 (开放式)
 $507万
 $23,045/呎
-(25年-07月)</t>
+(25年-07月-06日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -9261,7 +9261,7 @@
           <t>F | 293呎 (开放式)
 $630万
 $21,509/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -9269,7 +9269,7 @@
           <t>G | 266呎 (开放式)
 $538万
 $20,211/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -9277,7 +9277,7 @@
           <t>H | 252呎 (开放式)
 $509万
 $20,202/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -9285,7 +9285,7 @@
           <t>J | 211呎 (开放式)
 $427万
 $20,227/呎
-(24年-10月)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -9293,7 +9293,7 @@
           <t>K | 370呎 (1房)
 $856万
 $23,135/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
           <t>A | 524呎 (2房)
 $1457万
 $27,802/呎
-(24年-08月)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -9316,7 +9316,7 @@
           <t>B | 386呎 (1房)
 $1053万
 $27,272/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -9324,7 +9324,7 @@
           <t>C | 382呎 (1房)
 $990万
 $25,921/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -9332,7 +9332,7 @@
           <t>D | 297呎 (开放式)
 $804万
 $27,067/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -9340,7 +9340,7 @@
           <t>E | 220呎 (开放式)
 $516万
 $23,455/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -9348,7 +9348,7 @@
           <t>F | 294呎 (开放式)
 $626万
 $21,286/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -9356,7 +9356,7 @@
           <t>G | 266呎 (开放式)
 $533万
 $20,049/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -9364,7 +9364,7 @@
           <t>H | 252呎 (开放式)
 $506万
 $20,063/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -9372,7 +9372,7 @@
           <t>J | 211呎 (开放式)
 $428万
 $20,265/呎
-(24年-08月)</t>
+(24年-08月-06日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -9380,7 +9380,7 @@
           <t>K | 370呎 (1房)
 $866万
 $23,405/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
           <t>A | 524呎 (2房)
 $1461万
 $27,884/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -9403,7 +9403,7 @@
           <t>B | 386呎 (1房)
 $1050万
 $27,207/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -9411,7 +9411,7 @@
           <t>C | 382呎 (1房)
 $982万
 $25,712/呎
-(25年-01月)</t>
+(25年-01月-08日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -9419,7 +9419,7 @@
           <t>D | 297呎 (开放式)
 $777万
 $26,162/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -9427,7 +9427,7 @@
           <t>E | 220呎 (开放式)
 $500万
 $22,718/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -9435,7 +9435,7 @@
           <t>F | 293呎 (开放式)
 $621万
 $21,201/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -9443,7 +9443,7 @@
           <t>G | 266呎 (开放式)
 $530万
 $19,917/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -9451,7 +9451,7 @@
           <t>H | 252呎 (开放式)
 $501万
 $19,889/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -9459,7 +9459,7 @@
           <t>J | 211呎 (开放式)
 $420万
 $19,900/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -9467,7 +9467,7 @@
           <t>K | 370呎 (1房)
 $843万
 $22,784/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9482,7 @@
           <t>A | 524呎 (2房)
 $1435万
 $27,384/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -9490,7 +9490,7 @@
           <t>B | 386呎 (1房)
 $1033万
 $26,762/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -9498,7 +9498,7 @@
           <t>C | 382呎 (1房)
 $975万
 $25,531/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>D | 297呎 (开放式)
 $763万
 $25,690/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -9514,7 +9514,7 @@
           <t>E | 220呎 (开放式)
 $491万
 $22,309/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -9522,7 +9522,7 @@
           <t>F | 293呎 (开放式)
 $617万
 $21,051/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -9530,7 +9530,7 @@
           <t>G | 266呎 (开放式)
 $526万
 $19,756/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -9538,7 +9538,7 @@
           <t>H | 252呎 (开放式)
 $498万
 $19,754/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -9546,7 +9546,7 @@
           <t>J | 211呎 (开放式)
 $417万
 $19,782/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -9554,7 +9554,7 @@
           <t>K | 370呎 (1房)
 $836万
 $22,595/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
           <t>A | 524呎 (2房)
 $1424万
 $27,185/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -9577,7 +9577,7 @@
           <t>B | 386呎 (1房)
 $1024万
 $26,526/呎
-(25年-07月)</t>
+(25年-07月-20日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -9585,7 +9585,7 @@
           <t>C | 382呎 (1房)
 $968万
 $25,348/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -9593,7 +9593,7 @@
           <t>D | 297呎 (开放式)
 $757万
 $25,488/呎
-(25年-12月)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -9601,7 +9601,7 @@
           <t>E | 220呎 (开放式)
 $488万
 $22,173/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -9609,7 +9609,7 @@
           <t>F | 294呎 (开放式)
 $605万
 $20,588/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -9617,7 +9617,7 @@
           <t>G | 266呎 (开放式)
 $521万
 $19,590/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -9625,7 +9625,7 @@
           <t>H | 252呎 (开放式)
 $494万
 $19,611/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -9633,7 +9633,7 @@
           <t>J | 211呎 (开放式)
 $414万
 $19,611/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -9641,7 +9641,7 @@
           <t>K | 370呎 (1房)
 $830万
 $22,432/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9656,7 @@
           <t>A | 524呎 (2房)
 $1414万
 $26,985/呎
-(24年-07月)</t>
+(24年-07月-09日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -9664,7 +9664,7 @@
           <t>B | 386呎 (1房)
 $1017万
 $26,337/呎
-(25年-07月)</t>
+(25年-07月-27日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -9672,7 +9672,7 @@
           <t>C | 382呎 (1房)
 $960万
 $25,141/呎
-(25年-06月)</t>
+(25年-06月-01日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -9680,7 +9680,7 @@
           <t>D | 297呎 (开放式)
 $752万
 $25,320/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -9688,7 +9688,7 @@
           <t>E | 220呎 (开放式)
 $479万
 $21,773/呎
-(24年-08月)</t>
+(24年-08月-05日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -9696,7 +9696,7 @@
           <t>F | 293呎 (开放式)
 $601万
 $20,505/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -9704,7 +9704,7 @@
           <t>G | 266呎 (开放式)
 $518万
 $19,459/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -9712,7 +9712,7 @@
           <t>H | 252呎 (开放式)
 $495万
 $19,639/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -9720,7 +9720,7 @@
           <t>J | 211呎 (开放式)
 $411万
 $19,488/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -9728,7 +9728,7 @@
           <t>K | 370呎 (1房)
 $824万
 $22,270/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
           <t>A | 524呎 (2房)
 $1418万
 $27,057/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -9751,7 +9751,7 @@
           <t>B | 386呎 (1房)
 $1008万
 $26,122/呎
-(25年-07月)</t>
+(25年-07月-31日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -9759,7 +9759,7 @@
           <t>C | 382呎 (1房)
 $954万
 $24,961/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -9767,7 +9767,7 @@
           <t>D | 297呎 (开放式)
 $752万
 $25,320/呎
-(25年-05月)</t>
+(25年-05月-18日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -9775,7 +9775,7 @@
           <t>E | 220呎 (开放式)
 $475万
 $21,591/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -9783,7 +9783,7 @@
           <t>F | 293呎 (开放式)
 $596万
 $20,355/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -9791,7 +9791,7 @@
           <t>G | 266呎 (开放式)
 $514万
 $19,331/呎
-(24年-09月)</t>
+(24年-09月-08日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -9799,7 +9799,7 @@
           <t>H | 252呎 (开放式)
 $486万
 $19,306/呎
-(24年-07月)</t>
+(24年-07月-09日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -9807,7 +9807,7 @@
           <t>J | 211呎 (开放式)
 $408万
 $19,332/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -9815,7 +9815,7 @@
           <t>K | 370呎 (1房)
 $838万
 $22,657/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
           <t>A | 524呎 (2房)
 $1393万
 $26,586/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -9838,7 +9838,7 @@
           <t>B | 385呎 (1房)
 $1003万
 $26,047/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -9846,7 +9846,7 @@
           <t>C | 382呎 (1房)
 $946万
 $24,777/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -9854,7 +9854,7 @@
           <t>D | 297呎 (开放式)
 $746万
 $25,118/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -9862,7 +9862,7 @@
           <t>E | 220呎 (开放式)
 $472万
 $21,455/呎
-(24年-08月)</t>
+(24年-08月-14日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -9870,7 +9870,7 @@
           <t>F | 293呎 (开放式)
 $592万
 $20,201/呎
-(24年-07月)</t>
+(24年-07月-10日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -9878,7 +9878,7 @@
           <t>G | 266呎 (开放式)
 $510万
 $19,165/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -9886,7 +9886,7 @@
           <t>H | 252呎 (开放式)
 $483万
 $19,163/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -9894,7 +9894,7 @@
           <t>J | 211呎 (开放式)
 $405万
 $19,204/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -9902,7 +9902,7 @@
           <t>K | 370呎 (1房)
 $827万
 $22,359/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9917,7 @@
           <t>A | 524呎 (2房)
 $1362万
 $25,989/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9925,7 +9925,7 @@
           <t>B | 385呎 (1房)
 $1000万
 $25,969/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9933,7 +9933,7 @@
           <t>C | 382呎 (1房)
 $926万
 $24,233/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -9941,7 +9941,7 @@
           <t>D | 297呎 (开放式)
 $731万
 $24,626/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -9949,7 +9949,7 @@
           <t>E | 220呎 (开放式)
 $468万
 $21,273/呎
-(24年-08月)</t>
+(24年-08月-01日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -9957,7 +9957,7 @@
           <t>F | 294呎 (开放式)
 $588万
 $19,983/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -9965,7 +9965,7 @@
           <t>G | 266呎 (开放式)
 $506万
 $19,038/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -9973,7 +9973,7 @@
           <t>H | 252呎 (开放式)
 $484万
 $19,218/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -9981,7 +9981,7 @@
           <t>J | 211呎 (开放式)
 $402万
 $19,038/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -9989,7 +9989,7 @@
           <t>K | 370呎 (1房)
 $813万
 $21,978/呎
-(25年-09月)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
           <t>A | 524呎 (2房)
 $1351万
 $25,790/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -10012,7 +10012,7 @@
           <t>B | 386呎 (1房)
 $976万
 $25,298/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -10020,7 +10020,7 @@
           <t>C | 382呎 (1房)
 $919万
 $24,050/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -10028,7 +10028,7 @@
           <t>D | 297呎 (开放式)
 $724万
 $24,377/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -10036,7 +10036,7 @@
           <t>E | 220呎 (开放式)
 $465万
 $21,136/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -10044,7 +10044,7 @@
           <t>F | 293呎 (开放式)
 $583万
 $19,898/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -10052,7 +10052,7 @@
           <t>G | 266呎 (开放式)
 $502万
 $18,872/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -10060,7 +10060,7 @@
           <t>H | 252呎 (开放式)
 $476万
 $18,889/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -10068,7 +10068,7 @@
           <t>J | 211呎 (开放式)
 $398万
 $18,882/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -10076,7 +10076,7 @@
           <t>K | 370呎 (1房)
 $819万
 $22,141/呎
-(25年-09月)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10091,7 @@
           <t>A | 524呎 (2房)
 $1341万
 $25,590/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -10099,7 +10099,7 @@
           <t>B | 385呎 (1房)
 $965万
 $25,070/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -10107,7 +10107,7 @@
           <t>C | 382呎 (1房)
 $912万
 $23,872/呎
-(25年-10月)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -10115,7 +10115,7 @@
           <t>D | 297呎 (开放式)
 $713万
 $24,007/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -10123,7 +10123,7 @@
           <t>E | 220呎 (开放式)
 $461万
 $20,955/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -10131,7 +10131,7 @@
           <t>F | 294呎 (开放式)
 $579万
 $19,680/呎
-(24年-09月)</t>
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -10139,7 +10139,7 @@
           <t>G | 266呎 (开放式)
 $504万
 $18,932/呎
-(24年-07月)</t>
+(24年-07月-24日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -10147,7 +10147,7 @@
           <t>H | 252呎 (开放式)
 $472万
 $18,750/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -10155,7 +10155,7 @@
           <t>J | 211呎 (开放式)
 $400万
 $18,943/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -10163,7 +10163,7 @@
           <t>K | 370呎 (1房)
 $801万
 $21,651/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
           <t>A | 524呎 (2房)
 $1312万
 $25,032/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -10186,7 +10186,7 @@
           <t>B | 385呎 (1房)
 $943万
 $24,499/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -10194,7 +10194,7 @@
           <t>C | 382呎 (1房)
 $891万
 $23,322/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -10202,7 +10202,7 @@
           <t>D | 297呎 (开放式)
 $696万
 $23,434/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -10210,15 +10210,15 @@
           <t>E | 220呎 (开放式)
 $458万
 $20,818/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 293呎 (开放式)
+          <t>F | 294呎 (开放式)
 $575万
-$19,628/呎
-(24年-09月)</t>
+$19,561/呎
+(24年-09月-10日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -10226,7 +10226,7 @@
           <t>G | 266呎 (开放式)
 $495万
 $18,613/呎
-(24年-07月)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -10234,7 +10234,7 @@
           <t>H | 252呎 (开放式)
 $469万
 $18,615/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -10242,7 +10242,7 @@
           <t>J | 211呎 (开放式)
 $393万
 $18,630/呎
-(24年-07月)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -10250,7 +10250,7 @@
           <t>K | 370呎 (1房)
 $795万
 $21,486/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
           <t>A | 524呎 (2房)
 $1304万
 $24,893/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -10273,7 +10273,7 @@
           <t>B | 385呎 (1房)
 $939万
 $24,392/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -10281,7 +10281,7 @@
           <t>C | 382呎 (1房)
 $887万
 $23,220/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -10289,7 +10289,7 @@
           <t>D | 297呎 (开放式)
 $693万
 $23,333/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -10297,7 +10297,7 @@
           <t>E | 220呎 (开放式)
 $455万
 $20,682/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -10305,7 +10305,7 @@
           <t>F | 293呎 (开放式)
 $571万
 $19,502/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -10313,7 +10313,7 @@
           <t>G | 266呎 (开放式)
 $492万
 $18,515/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -10321,7 +10321,7 @@
           <t>H | 252呎 (开放式)
 $471万
 $18,698/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -10329,7 +10329,7 @@
           <t>J | 211呎 (开放式)
 $394万
 $18,697/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -10337,7 +10337,7 @@
           <t>K | 370呎 (1房)
 $791万
 $21,378/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
           <t>B | 375呎 (1房)
 $886万
 $23,627/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -10368,7 +10368,7 @@
           <t>C | 369呎 (1房)
 $874万
 $23,686/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -10376,7 +10376,7 @@
           <t>D | 286呎 (开放式)
 $773万
 $27,031/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -10384,7 +10384,7 @@
           <t>E | 206呎 (开放式)
 $520万
 $25,243/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -10392,7 +10392,7 @@
           <t>F | 294呎 (开放式)
 $569万
 $19,350/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -10400,7 +10400,7 @@
           <t>G | 266呎 (开放式)
 $488万
 $18,353/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -10408,7 +10408,7 @@
           <t>H | 252呎 (开放式)
 $464万
 $18,405/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -10416,7 +10416,7 @@
           <t>J | 211呎 (开放式)
 $393万
 $18,611/呎
-(24年-07月)</t>
+(24年-07月-07日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr"/>
